--- a/docs/SEO_MASTER_Casa_Pratica.xlsx
+++ b/docs/SEO_MASTER_Casa_Pratica.xlsx
@@ -225,8 +225,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MasterSEO" displayName="MasterSEO" ref="A1:S13" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A1:S13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MasterSEO" displayName="MasterSEO" ref="A1:S14" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A1:S14"/>
   <tableColumns count="19">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Grupo / Silo"/>
@@ -276,8 +276,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="HistoricoAcoes" displayName="HistoricoAcoes" ref="A1:J3" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A1:J2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="HistoricoAcoes" displayName="HistoricoAcoes" ref="A1:J7" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A1:J7"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Data"/>
     <tableColumn id="2" name="ID"/>
@@ -583,7 +583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -831,7 +831,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Acompanhar</t>
+          <t>Otimizar</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -841,24 +841,36 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Em monitoramento</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="n"/>
-      <c r="N3" s="3" t="n"/>
+          <t>Alterado / monitorando</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="n">
+        <v>46268</v>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>SEO on-page — Etapa 1</t>
+        </is>
+      </c>
       <c r="O3" s="4">
         <f>IF([@[Última alteração]]="","",[@[Última alteração]]+28)</f>
         <v/>
       </c>
-      <c r="P3" s="3" t="n"/>
-      <c r="Q3" s="3" t="n"/>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>Alteração realizada</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>62</v>
+      </c>
       <c r="R3" s="3">
         <f>IF(OR([@[Posição atual]]="",[@[Posição anterior]]=""),"",[@[Posição anterior]]-[@[Posição atual]])</f>
         <v/>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>Intenção comercial específica.</t>
+          <t>Etapa 1 — consolidação da intenção custo-benefício/preço-performance. Home permanece dona do ranking geral de melhores fogões 5 bocas. Intervenção limitada a title e meta description. Aguardar recrawl/GSC antes de nova intervenção.</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1269,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Mapear</t>
+          <t>Otimizar</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -1267,16 +1279,26 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Mapeado</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="n"/>
-      <c r="N9" s="3" t="n"/>
+          <t>Alterado / monitorando</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>46268</v>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>SEO on-page — Etapa 1</t>
+        </is>
+      </c>
       <c r="O9" s="4">
         <f>IF([@[Última alteração]]="","",[@[Última alteração]]+28)</f>
         <v/>
       </c>
-      <c r="P9" s="3" t="n"/>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Alteração realizada</t>
+        </is>
+      </c>
       <c r="Q9" s="3" t="n"/>
       <c r="R9" s="3">
         <f>IF(OR([@[Posição atual]]="",[@[Posição anterior]]=""),"",[@[Posição anterior]]-[@[Posição atual]])</f>
@@ -1284,7 +1306,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>Decisão comparativa entre materiais.</t>
+          <t>Etapa 1 — alterados somente title e meta description para consolidar a intenção "fogão com mesa de vidro ou inox". Blog /blog/fogao-mesa-de-vidro-ou-inox/ permanece URL dona da comparação vidro × inox; hub /melhores/melhor-fogao-mesa-de-vidro/ permanece dono de “melhor fogão mesa de vidro”. Aguardar recrawl/GSC antes de nova intervenção.</t>
         </is>
       </c>
     </row>
@@ -1549,6 +1571,91 @@
       <c r="S13" s="3" t="inlineStr">
         <is>
           <t>Consulta ampla; precisa de contexto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Segurança / risco — mesa de vidro</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>fogão com mesa de vidro é perigoso</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>fogão com mesa de vidro é seguro?; pode estourar</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>/blog/fogao-mesa-de-vidro-seguro/</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>/blog/fogao-mesa-de-vidro-seguro/</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Otimizar</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Alterado / monitorando</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>46268</v>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>SEO on-page — Etapa 1</t>
+        </is>
+      </c>
+      <c r="O14" s="4">
+        <f>IF([@[Última alteração]]="","",[@[Última alteração]]+28)</f>
+        <v/>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Alteração realizada</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="R14" s="3">
+        <f>IF(OR([@[Posição atual]]="",[@[Posição anterior]]=""),"",[@[Posição anterior]]-[@[Posição atual]])</f>
+        <v/>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t>Etapa 1 executada somente em title e meta description para consolidar a intenção de segurança/risco (“é perigoso”). Página já existente e dona da intenção. Comparativo vidro × inox permanece separado como intenção de comparação; hub mesa de vidro permanece dono do ranking. Aguardar recrawl/GSC antes de nova intervenção.</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1963,6 +2070,132 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>Variação volume: keyword principal 590 (tamanho fogão 5 bocas) + variação 90 (tamanho do fogão 5 bocas). Próxima revisão: ~01/10/2026. Sem commit/push/deploy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>melhor fogao 5 bocas custo beneficio</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>/fogao-5-bocas-custo-beneficio/</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SEO on-page — Etapa 1</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>62</v>
+      </c>
+      <c r="G5" t="n">
+        <v>62</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Title e meta description da página otimizados para consolidar a intenção de custo-benefício/preço-performance.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Alteração realizada</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Home permanece dona de “melhores fogões 5 bocas”; esta URL permanece dona da intenção específica de custo-benefício. Aguardar recrawl/GSC antes de nova intervenção.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>fogão com mesa de vidro ou inox</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>/blog/fogao-mesa-de-vidro-ou-inox/</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SEO on-page — Etapa 1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>title e meta description</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Alteração realizada</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>comparação vidro × inox permanece separada do ranking de melhores fogões com mesa de vidro; aguardar recrawl/GSC antes de nova intervenção.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B7" t="n">
+        <v>13</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>fogão com mesa de vidro é perigoso</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>/blog/fogao-mesa-de-vidro-seguro/</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SEO on-page — Etapa 1</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>13</v>
+      </c>
+      <c r="G7" t="n">
+        <v>13</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Title + meta description</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Alteração realizada</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Consolidação da intenção de segurança/risco; comparativo vidro × inox e hub de ranking permanecem com suas respectivas intenções.</t>
         </is>
       </c>
     </row>

--- a/docs/SEO_MASTER_Casa_Pratica.xlsx
+++ b/docs/SEO_MASTER_Casa_Pratica.xlsx
@@ -93,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -117,6 +117,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -276,8 +277,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="HistoricoAcoes" displayName="HistoricoAcoes" ref="A1:J7" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A1:J7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="HistoricoAcoes" displayName="HistoricoAcoes" ref="A1:J8" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A1:J8"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Data"/>
     <tableColumn id="2" name="ID"/>
@@ -1358,24 +1359,36 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Mapeado</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="n"/>
-      <c r="N10" s="3" t="n"/>
+          <t>Alterado / monitorando</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>46268</v>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>SEO on-page — Etapa 2</t>
+        </is>
+      </c>
       <c r="O10" s="4">
         <f>IF([@[Última alteração]]="","",[@[Última alteração]]+28)</f>
         <v/>
       </c>
-      <c r="P10" s="3" t="n"/>
-      <c r="Q10" s="3" t="n"/>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Alteração realizada</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>46</v>
+      </c>
       <c r="R10" s="3">
         <f>IF(OR([@[Posição atual]]="",[@[Posição anterior]]=""),"",[@[Posição anterior]]-[@[Posição atual]])</f>
         <v/>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>Categoria diferente de 5 bocas.</t>
+          <t>Etapa 2: FAQ visível + FAQPage sobre custo-benefício. Title/H1/meta/canonical preservados. Não altera ownership do hub melhor fogão 4 bocas. Aguardar GSC.</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2196,6 +2209,50 @@
       <c r="J7" t="inlineStr">
         <is>
           <t>Consolidação da intenção de segurança/risco; comparativo vidro × inox e hub de ranking permanecem com suas respectivas intenções.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>fogão 4 bocas custo benefício</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>/fogao-4-bocas-custo-beneficio/</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SEO on-page — Etapa 2</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>46</v>
+      </c>
+      <c r="G8" t="n">
+        <v>46</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>FAQ visível + FAQPage</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Alteração realizada</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Etapa 2: FAQ visível + FAQPage sobre custo-benefício. Title/H1/meta/canonical preservados. Não altera ownership do hub melhor fogão 4 bocas. Aguardar GSC.</t>
         </is>
       </c>
     </row>

--- a/docs/SEO_MASTER_Casa_Pratica.xlsx
+++ b/docs/SEO_MASTER_Casa_Pratica.xlsx
@@ -1,30 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MASTER SEO" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ENTRADAS SEMRUSH" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CALENDÁRIO" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="HISTÓRICO" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="LEIA-ME" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MASTER SEO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENTRADAS SEMRUSH" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CALENDÁRIO" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HISTÓRICO" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEIA-ME" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ESTUDO CAMPO 2026-09-05" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MASTER SEO'!$A$1:$S$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ENTRADAS SEMRUSH'!$A$1:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CALENDÁRIO'!$A$1:$G$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HISTÓRICO'!$A$1:$J$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LEIA-ME'!$A$1:$B$9</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,28 +41,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -64,6 +62,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -76,15 +84,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00D1D5DB"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D1D5DB"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D1D5DB"/>
-      </top>
       <bottom style="thin">
         <color rgb="00D1D5DB"/>
       </bottom>
@@ -93,31 +92,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -208,91 +212,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Casa Prática Eletro</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>Cada nova exportação recebe um ID de lote inédito (ex.: SM-AAAA-MM-DD). Nunca sobrescrever linhas de lotes anteriores.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MasterSEO" displayName="MasterSEO" ref="A1:S14" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A1:S14"/>
-  <tableColumns count="19">
-    <tableColumn id="1" name="ID"/>
-    <tableColumn id="2" name="Grupo / Silo"/>
-    <tableColumn id="3" name="Keyword principal"/>
-    <tableColumn id="4" name="Variações"/>
-    <tableColumn id="5" name="Intenção"/>
-    <tableColumn id="6" name="Volume"/>
-    <tableColumn id="7" name="Posição atual"/>
-    <tableColumn id="8" name="URL atual"/>
-    <tableColumn id="9" name="URL dona / alvo"/>
-    <tableColumn id="10" name="Decisão"/>
-    <tableColumn id="11" name="Prioridade"/>
-    <tableColumn id="12" name="Status"/>
-    <tableColumn id="13" name="Última alteração"/>
-    <tableColumn id="14" name="Tipo de alteração"/>
-    <tableColumn id="15" name="Próxima revisão">
-      <calculatedColumnFormula>IF([Última alteração]="","",[Última alteração]+28)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="16" name="Resultado da revisão"/>
-    <tableColumn id="17" name="Posição anterior"/>
-    <tableColumn id="18" name="Variação posição">
-      <calculatedColumnFormula>IF(OR([Posição atual]="",[Posição anterior]=""),"",[Posição anterior]-[Posição atual])</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="19" name="Observações"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EntradasSemrush" displayName="EntradasSemrush" ref="A1:J2" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A1:J2"/>
-  <tableColumns count="10">
-    <tableColumn id="1" name="ID do lote"/>
-    <tableColumn id="2" name="Data da exportação"/>
-    <tableColumn id="3" name="Keyword"/>
-    <tableColumn id="4" name="Posição"/>
-    <tableColumn id="5" name="Volume"/>
-    <tableColumn id="6" name="KD"/>
-    <tableColumn id="7" name="Intenção"/>
-    <tableColumn id="8" name="URL encontrada pelo Semrush"/>
-    <tableColumn id="9" name="SERP Features"/>
-    <tableColumn id="10" name="Observações"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="HistoricoAcoes" displayName="HistoricoAcoes" ref="A1:J8" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A1:J8"/>
-  <tableColumns count="10">
-    <tableColumn id="1" name="Data"/>
-    <tableColumn id="2" name="ID"/>
-    <tableColumn id="3" name="Keyword"/>
-    <tableColumn id="4" name="URL"/>
-    <tableColumn id="5" name="Evento"/>
-    <tableColumn id="6" name="Posição antes"/>
-    <tableColumn id="7" name="Posição depois"/>
-    <tableColumn id="8" name="Alteração realizada"/>
-    <tableColumn id="9" name="Resultado"/>
-    <tableColumn id="10" name="Observações"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -584,20 +503,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
@@ -608,7 +527,7 @@
     <col width="55" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
@@ -709,22 +628,22 @@
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Melhor fogão 5 bocas</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>melhor fogao 5 bocas</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>melhores fogoes 5 bocas; melhores fogoes de 5 bocas; melhor fogão de 5 bocas; qual é o melhor fogao de 5 bocas; qual melhor fogao 5 bocas; fogão 5 bocas bom</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Investigação comercial</t>
         </is>
@@ -735,58 +654,46 @@
       <c r="G2" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>/melhores-fogoes-5-bocas/</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>/melhores-fogoes-5-bocas/</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Otimizar</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>Alterado / monitorando</t>
-        </is>
-      </c>
-      <c r="M2" s="4" t="n">
-        <v>46268</v>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>SEO on-page — Etapa 1</t>
-        </is>
-      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Em monitoramento</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="n"/>
+      <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="4">
-        <f>IF([@[Última alteração]]="","",[@[Última alteração]]+28)</f>
-        <v/>
-      </c>
-      <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>Alteração realizada</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="R2" s="3">
-        <f>IF(OR([@[Posição atual]]="",[@[Posição anterior]]=""),"",[@[Posição anterior]]-[@[Posição atual]])</f>
-        <v/>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>Home consolidada como dona da intenção 'melhor fogão 5 bocas'. Etapa 1 limitada a title + meta description; OG/Twitter derivados. Hub /melhores/melhor-fogao-5-bocas/ permanece 301 → /. Não reabrir o hub por persistência histórica no Semrush. Aguardar recrawl/nova medição antes de nova intervenção.</t>
+        <f>IF(M2="","",M2+28)</f>
+        <v/>
+      </c>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2">
+        <f>IF(OR(G2="",Q2=""),"",Q2-G2)</f>
+        <v/>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>Hub/ranking principal.</t>
         </is>
       </c>
     </row>
@@ -794,22 +701,22 @@
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Fogão 5 bocas custo-benefício</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>melhor fogao 5 bocas custo beneficio</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>fogao 5 bocas melhor custo beneficio; fogão 5 bocas bom e barato</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Investigação comercial</t>
         </is>
@@ -820,58 +727,46 @@
       <c r="G3" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>/fogao-5-bocas-custo-beneficio/</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>/fogao-5-bocas-custo-beneficio/</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>Otimizar</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Acompanhar</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>Alterado / monitorando</t>
-        </is>
-      </c>
-      <c r="M3" s="7" t="n">
-        <v>46268</v>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>SEO on-page — Etapa 1</t>
-        </is>
-      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Em monitoramento</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="4">
-        <f>IF([@[Última alteração]]="","",[@[Última alteração]]+28)</f>
-        <v/>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>Alteração realizada</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="R3" s="3">
-        <f>IF(OR([@[Posição atual]]="",[@[Posição anterior]]=""),"",[@[Posição anterior]]-[@[Posição atual]])</f>
-        <v/>
-      </c>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>Etapa 1 — consolidação da intenção custo-benefício/preço-performance. Home permanece dona do ranking geral de melhores fogões 5 bocas. Intervenção limitada a title e meta description. Aguardar recrawl/GSC antes de nova intervenção.</t>
+        <f>IF(M3="","",M3+28)</f>
+        <v/>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2">
+        <f>IF(OR(G3="",Q3=""),"",Q3-G3)</f>
+        <v/>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>Intenção comercial específica.</t>
         </is>
       </c>
     </row>
@@ -879,84 +774,72 @@
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Tamanho do fogão 5 bocas</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>tamanho do fogao 5 bocas</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>tamanho fogão 5 bocas</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Informacional</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>590</v>
+        <v>90</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>/como-escolher-fogao-5-bocas/</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>/como-escolher-fogao-5-bocas/</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Otimizar</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>Alterado / monitorando</t>
-        </is>
-      </c>
-      <c r="M4" s="7" t="n">
-        <v>46268</v>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>SEO on-page — Etapa 1 + conteúdo</t>
-        </is>
-      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>/melhores-fogoes-5-bocas/</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>/melhores-fogoes-5-bocas/</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Avaliar</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Mapeado</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="4">
-        <f>IF([@[Última alteração]]="","",[@[Última alteração]]+28)</f>
-        <v/>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>Alteração realizada — aguardando nova medição</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="R4" s="3">
-        <f>IF(OR([@[Posição atual]]="",[@[Posição anterior]]=""),"",[@[Posição anterior]]-[@[Posição atual]])</f>
-        <v/>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>Intenção: tamanho fogão 5 bocas (590) + tamanho do fogão 5 bocas (90). Title ajustado para priorizar tamanho/medidas. Meta description com valores típicos (75-80 cm / 60-70 cm / ~90 cm). Resposta direta e tabela de medidas inseridas no step 1. H1 e estrutura preservados. Dados reutilizados do blog /blog/fogao-5-bocas-reduz-espaco-cozinha/. Build 29 págs, exit 0. Sem commit/push/deploy.</t>
+        <f>IF(M4="","",M4+28)</f>
+        <v/>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="n"/>
+      <c r="R4" s="2">
+        <f>IF(OR(G4="",Q4=""),"",Q4-G4)</f>
+        <v/>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>Avaliar a URL atual antes de criar artigo.</t>
         </is>
       </c>
     </row>
@@ -964,22 +847,22 @@
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Melhor marca de fogão 5 bocas</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>melhor marca de fogão 5 bocas</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>qual a melhor marca de fogão 5 bocas; melhores marcas de fogão 5 bocas</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Investigação comercial</t>
         </is>
@@ -990,44 +873,44 @@
       <c r="G5" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>/melhores-fogoes-5-bocas/</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>/melhores-fogoes-5-bocas/</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Avaliar</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Mapeado</t>
         </is>
       </c>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="4">
-        <f>IF([@[Última alteração]]="","",[@[Última alteração]]+28)</f>
-        <v/>
-      </c>
-      <c r="P5" s="3" t="n"/>
-      <c r="Q5" s="3" t="n"/>
-      <c r="R5" s="3">
-        <f>IF(OR([@[Posição atual]]="",[@[Posição anterior]]=""),"",[@[Posição anterior]]-[@[Posição atual]])</f>
-        <v/>
-      </c>
-      <c r="S5" s="3" t="inlineStr">
+        <f>IF(M5="","",M5+28)</f>
+        <v/>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="n"/>
+      <c r="R5" s="2">
+        <f>IF(OR(G5="",Q5=""),"",Q5-G5)</f>
+        <v/>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>Verificar arquitetura antes de nova URL.</t>
         </is>
@@ -1037,58 +920,58 @@
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Fogão Consul é bom</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>fogao consul é bom</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Investigação comercial</t>
         </is>
       </c>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>/review-fogao-mesa-de-vidro-consul/</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Mapear</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>Mapeado</t>
         </is>
       </c>
-      <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="4">
-        <f>IF([@[Última alteração]]="","",[@[Última alteração]]+28)</f>
-        <v/>
-      </c>
-      <c r="P6" s="3" t="n"/>
-      <c r="Q6" s="3" t="n"/>
-      <c r="R6" s="3">
-        <f>IF(OR([@[Posição atual]]="",[@[Posição anterior]]=""),"",[@[Posição anterior]]-[@[Posição atual]])</f>
-        <v/>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
+        <f>IF(M6="","",M6+28)</f>
+        <v/>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="n"/>
+      <c r="R6" s="2">
+        <f>IF(OR(G6="",Q6=""),"",Q6-G6)</f>
+        <v/>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>Não confundir com Consul + mesa de vidro.</t>
         </is>
@@ -1098,18 +981,18 @@
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Fogão Consul mesa de vidro</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>fogao consul mesa de vidro</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Investigação comercial</t>
         </is>
@@ -1120,27 +1003,27 @@
       <c r="G7" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>/review-fogao-mesa-de-vidro-consul/</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>/review-fogao-mesa-de-vidro-consul/</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Otimizar</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>Alterado / monitorando</t>
         </is>
@@ -1148,16 +1031,16 @@
       <c r="M7" s="4" t="n">
         <v>46267</v>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>SEO on-page</t>
         </is>
       </c>
       <c r="O7" s="4">
-        <f>IF([@[Última alteração]]="","",[@[Última alteração]]+28)</f>
-        <v/>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
+        <f>IF(M7="","",M7+28)</f>
+        <v/>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>Alteração realizada</t>
         </is>
@@ -1165,11 +1048,11 @@
       <c r="Q7" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="R7" s="3">
-        <f>IF(OR([@[Posição atual]]="",[@[Posição anterior]]=""),"",[@[Posição anterior]]-[@[Posição atual]])</f>
-        <v/>
-      </c>
-      <c r="S7" s="3" t="inlineStr">
+      <c r="R7" s="2">
+        <f>IF(OR(G7="",Q7=""),"",Q7-G7)</f>
+        <v/>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>Aguardar indexação antes de nova intervenção.</t>
         </is>
@@ -1179,62 +1062,62 @@
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Fogão com mesa de vidro</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>fogao com mesa de vidro</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Investigação comercial</t>
         </is>
       </c>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>/review-fogao-mesa-de-vidro-consul/</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>/melhores-fogoes-mesa-de-vidro/</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Mapear</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>Mapeado</t>
         </is>
       </c>
-      <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="4">
-        <f>IF([@[Última alteração]]="","",[@[Última alteração]]+28)</f>
-        <v/>
-      </c>
-      <c r="P8" s="3" t="n"/>
-      <c r="Q8" s="3" t="n"/>
-      <c r="R8" s="3">
-        <f>IF(OR([@[Posição atual]]="",[@[Posição anterior]]=""),"",[@[Posição anterior]]-[@[Posição atual]])</f>
-        <v/>
-      </c>
-      <c r="S8" s="3" t="inlineStr">
+        <f>IF(M8="","",M8+28)</f>
+        <v/>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="n"/>
+      <c r="R8" s="2">
+        <f>IF(OR(G8="",Q8=""),"",Q8-G8)</f>
+        <v/>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>Intenção genérica deve pertencer ao hub.</t>
         </is>
@@ -1244,70 +1127,60 @@
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Mesa de vidro ou inox</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>fogão com mesa de vidro ou inox</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Informacional / comparação</t>
         </is>
       </c>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>/melhores-fogoes-mesa-de-vidro/</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>Otimizar</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Mapear</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>Alterado / monitorando</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="n">
-        <v>46268</v>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>SEO on-page — Etapa 1</t>
-        </is>
-      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Mapeado</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="4">
-        <f>IF([@[Última alteração]]="","",[@[Última alteração]]+28)</f>
-        <v/>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t>Alteração realizada</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="n"/>
-      <c r="R9" s="3">
-        <f>IF(OR([@[Posição atual]]="",[@[Posição anterior]]=""),"",[@[Posição anterior]]-[@[Posição atual]])</f>
-        <v/>
-      </c>
-      <c r="S9" s="3" t="inlineStr">
-        <is>
-          <t>Etapa 1 — alterados somente title e meta description para consolidar a intenção "fogão com mesa de vidro ou inox". Blog /blog/fogao-mesa-de-vidro-ou-inox/ permanece URL dona da comparação vidro × inox; hub /melhores/melhor-fogao-mesa-de-vidro/ permanece dono de “melhor fogão mesa de vidro”. Aguardar recrawl/GSC antes de nova intervenção.</t>
+        <f>IF(M9="","",M9+28)</f>
+        <v/>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="n"/>
+      <c r="R9" s="2">
+        <f>IF(OR(G9="",Q9=""),"",Q9-G9)</f>
+        <v/>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>Decisão comparativa entre materiais.</t>
         </is>
       </c>
     </row>
@@ -1315,18 +1188,18 @@
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Fogão 4 bocas custo-benefício</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>fogão 4 bocas custo benefício</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Investigação comercial</t>
         </is>
@@ -1337,58 +1210,46 @@
       <c r="G10" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>/fogao-4-bocas-custo-beneficio/</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>/fogao-4-bocas-custo-beneficio/</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Acompanhar</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>Alterado / monitorando</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v>46268</v>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>SEO on-page — Etapa 2</t>
-        </is>
-      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Mapeado</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="n"/>
+      <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="4">
-        <f>IF([@[Última alteração]]="","",[@[Última alteração]]+28)</f>
-        <v/>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t>Alteração realizada</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="R10" s="3">
-        <f>IF(OR([@[Posição atual]]="",[@[Posição anterior]]=""),"",[@[Posição anterior]]-[@[Posição atual]])</f>
-        <v/>
-      </c>
-      <c r="S10" s="3" t="inlineStr">
-        <is>
-          <t>Etapa 2: FAQ visível + FAQPage sobre custo-benefício. Title/H1/meta/canonical preservados. Não altera ownership do hub melhor fogão 4 bocas. Aguardar GSC.</t>
+        <f>IF(M10="","",M10+28)</f>
+        <v/>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="n"/>
+      <c r="R10" s="2">
+        <f>IF(OR(G10="",Q10=""),"",Q10-G10)</f>
+        <v/>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>Categoria diferente de 5 bocas.</t>
         </is>
       </c>
     </row>
@@ -1396,18 +1257,18 @@
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Modelo BFS5NCR</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>bfs5ncr</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Navegacional</t>
         </is>
@@ -1418,40 +1279,40 @@
       <c r="G11" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Mapear</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>Mapeado</t>
         </is>
       </c>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="4">
-        <f>IF([@[Última alteração]]="","",[@[Última alteração]]+28)</f>
-        <v/>
-      </c>
-      <c r="P11" s="3" t="n"/>
-      <c r="Q11" s="3" t="n"/>
-      <c r="R11" s="3">
-        <f>IF(OR([@[Posição atual]]="",[@[Posição anterior]]=""),"",[@[Posição anterior]]-[@[Posição atual]])</f>
-        <v/>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
+        <f>IF(M11="","",M11+28)</f>
+        <v/>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="n"/>
+      <c r="R11" s="2">
+        <f>IF(OR(G11="",Q11=""),"",Q11-G11)</f>
+        <v/>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>Busca por código de modelo/SKU.</t>
         </is>
@@ -1461,18 +1322,18 @@
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Comparativo de eletrodomésticos</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>comparativo de eletrodomésticos</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Informacional / comparação</t>
         </is>
@@ -1483,40 +1344,40 @@
       <c r="G12" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Avaliar</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Mapeado</t>
         </is>
       </c>
-      <c r="M12" s="3" t="n"/>
-      <c r="N12" s="3" t="n"/>
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="4">
-        <f>IF([@[Última alteração]]="","",[@[Última alteração]]+28)</f>
-        <v/>
-      </c>
-      <c r="P12" s="3" t="n"/>
-      <c r="Q12" s="3" t="n"/>
-      <c r="R12" s="3">
-        <f>IF(OR([@[Posição atual]]="",[@[Posição anterior]]=""),"",[@[Posição anterior]]-[@[Posição atual]])</f>
-        <v/>
-      </c>
-      <c r="S12" s="3" t="inlineStr">
+        <f>IF(M12="","",M12+28)</f>
+        <v/>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="n"/>
+      <c r="R12" s="2">
+        <f>IF(OR(G12="",Q12=""),"",Q12-G12)</f>
+        <v/>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>Consulta genérica; não atribuir automaticamente ao silo de fogões.</t>
         </is>
@@ -1526,18 +1387,18 @@
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Eletrodoméstico com melhor avaliação</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>eletrodoméstico com melhor avaliação</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Investigação comercial</t>
         </is>
@@ -1548,40 +1409,40 @@
       <c r="G13" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Avaliar</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>Mapeado</t>
         </is>
       </c>
-      <c r="M13" s="3" t="n"/>
-      <c r="N13" s="3" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="4">
-        <f>IF([@[Última alteração]]="","",[@[Última alteração]]+28)</f>
-        <v/>
-      </c>
-      <c r="P13" s="3" t="n"/>
-      <c r="Q13" s="3" t="n"/>
-      <c r="R13" s="3">
-        <f>IF(OR([@[Posição atual]]="",[@[Posição anterior]]=""),"",[@[Posição anterior]]-[@[Posição atual]])</f>
-        <v/>
-      </c>
-      <c r="S13" s="3" t="inlineStr">
+        <f>IF(M13="","",M13+28)</f>
+        <v/>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="n"/>
+      <c r="R13" s="2">
+        <f>IF(OR(G13="",Q13=""),"",Q13-G13)</f>
+        <v/>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>Consulta ampla; precisa de contexto.</t>
         </is>
@@ -1589,91 +1450,141 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Segurança / risco — mesa de vidro</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>fogão com mesa de vidro é perigoso</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>fogão com mesa de vidro é seguro?; pode estourar</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Informacional</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>/blog/fogao-mesa-de-vidro-seguro/</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>/blog/fogao-mesa-de-vidro-seguro/</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>Otimizar</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
+        <v>14</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Mesa de vidro</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>como escolher fogão mesa de vidro</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>como escolher fogão com mesa de vidro; como escolher fogão de mesa de vidro</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Informacional → investigação comercial</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>/como-escolher-fogao-mesa-de-vidro/</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Criar</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>Alterado / monitorando</t>
-        </is>
-      </c>
-      <c r="M14" s="7" t="n">
-        <v>46268</v>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>SEO on-page — Etapa 1</t>
-        </is>
-      </c>
-      <c r="O14" s="4">
-        <f>IF([@[Última alteração]]="","",[@[Última alteração]]+28)</f>
-        <v/>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t>Alteração realizada</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="R14" s="3">
-        <f>IF(OR([@[Posição atual]]="",[@[Posição anterior]]=""),"",[@[Posição anterior]]-[@[Posição atual]])</f>
-        <v/>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t>Etapa 1 executada somente em title e meta description para consolidar a intenção de segurança/risco (“é perigoso”). Página já existente e dona da intenção. Comparativo vidro × inox permanece separado como intenção de comparação; hub mesa de vidro permanece dono do ranking. Aguardar recrawl/GSC antes de nova intervenção.</t>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Planejado</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>46270</v>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Decisão estratégica — estudo de campo</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P14" s="2" t="n"/>
+      <c r="Q14" s="2" t="n"/>
+      <c r="R14" s="2" t="n"/>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>Nova URL de satélite de critérios pré-compra. Evidência: cluster mesa de vidro já tem forte aderência no GSC; concorrentes editoriais usam páginas de critérios; SERP apresenta AI Overview, PAA, vídeos, editoriais e produtos. Não usar 'melhor fogão mesa de vidro' como eixo do title/H1 para evitar disputa com o hub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Mesa de vidro</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>fogão mesa de vidro custo benefício</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>fogão com mesa de vidro custo benefício; fogão mesa de vidro bom e barato</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Investigação comercial</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>/fogao-mesa-de-vidro-custo-beneficio/</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Criar</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Planejado</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>46270</v>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Decisão estratégica — estudo de campo</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P15" s="2" t="n"/>
+      <c r="Q15" s="2" t="n"/>
+      <c r="R15" s="2" t="n"/>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>Nova URL de satélite de valor. Intenção separada do ranking de mesa de vidro e complementar ao satélite de critérios. Volume específico não foi confirmado no lote; decisão baseada em convergência de arquitetura, concorrentes, SERP e caminho comercial. Title/H1 devem ser de valor, não 'melhor fogão'.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="O2:O5000">
+  <autoFilter ref="A1:S13"/>
+  <conditionalFormatting sqref="O2:O500">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND($O2&lt;&gt;"",$O2&lt;=TODAY(),$L2&lt;&gt;"Concluído")</formula>
     </cfRule>
@@ -1682,20 +1593,17 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="J2:J5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Criar página,Otimizar,Acompanhar,Avaliar,Mapear,Consolidar,Não fazer"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K2:K5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Alta,Média,Baixa"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Mapeado,Planejado,Alterado / monitorando,Em monitoramento,Concluído,Arquivado"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Criar página,Otimizar,Acompanhar,Avaliar,Mapear,Consolidar,Não fazer"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -1705,101 +1613,87 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ID do lote</t>
+          <t>Data da exportação</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Data da exportação</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Posição</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Posição</t>
+          <t>Volume</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Volume</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>Intenção</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Intenção</t>
+          <t>URL</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>URL encontrada pelo Semrush</t>
+          <t>SERP Features</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>SERP Features</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
           <t>Observações</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>SM-2026-09-01</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n">
+      <c r="A2" s="4" t="n">
         <v>46266</v>
       </c>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Cole novas exportações abaixo; não sobrescreva entradas antigas.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -1809,20 +1703,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Data da revisão</t>
@@ -1856,27 +1749,449 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-      <c r="I1" s="5" t="inlineStr">
-        <is>
-          <t>Agenda automática a partir da tabela MasterSEO. Não editar A2:G. Exige Microsoft 365.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4">
-        <f>IFERROR(SORT(FILTER(HSTACK(MasterSEO[[Próxima revisão]],MasterSEO[ID],MasterSEO[[Keyword principal]],IF(ISTEXT(MasterSEO[[URL dona / alvo]]),MasterSEO[[URL dona / alvo]],""),MasterSEO[Decisão],MasterSEO[Prioridade],MasterSEO[Status]),MasterSEO[[Próxima revisão]]&lt;&gt;""),1,1),"")</f>
-        <v/>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
+        <f>'MASTER SEO'!O2</f>
+        <v/>
+      </c>
+      <c r="B2" s="2">
+        <f>'MASTER SEO'!A2</f>
+        <v/>
+      </c>
+      <c r="C2" s="2">
+        <f>'MASTER SEO'!C2</f>
+        <v/>
+      </c>
+      <c r="D2" s="2">
+        <f>'MASTER SEO'!I2</f>
+        <v/>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Revisão programada</t>
+        </is>
+      </c>
+      <c r="F2" s="2">
+        <f>'MASTER SEO'!K2</f>
+        <v/>
+      </c>
+      <c r="G2" s="2">
+        <f>'MASTER SEO'!L2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4">
+        <f>'MASTER SEO'!O3</f>
+        <v/>
+      </c>
+      <c r="B3" s="2">
+        <f>'MASTER SEO'!A3</f>
+        <v/>
+      </c>
+      <c r="C3" s="2">
+        <f>'MASTER SEO'!C3</f>
+        <v/>
+      </c>
+      <c r="D3" s="2">
+        <f>'MASTER SEO'!I3</f>
+        <v/>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Revisão programada</t>
+        </is>
+      </c>
+      <c r="F3" s="2">
+        <f>'MASTER SEO'!K3</f>
+        <v/>
+      </c>
+      <c r="G3" s="2">
+        <f>'MASTER SEO'!L3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4">
+        <f>'MASTER SEO'!O4</f>
+        <v/>
+      </c>
+      <c r="B4" s="2">
+        <f>'MASTER SEO'!A4</f>
+        <v/>
+      </c>
+      <c r="C4" s="2">
+        <f>'MASTER SEO'!C4</f>
+        <v/>
+      </c>
+      <c r="D4" s="2">
+        <f>'MASTER SEO'!I4</f>
+        <v/>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Revisão programada</t>
+        </is>
+      </c>
+      <c r="F4" s="2">
+        <f>'MASTER SEO'!K4</f>
+        <v/>
+      </c>
+      <c r="G4" s="2">
+        <f>'MASTER SEO'!L4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4">
+        <f>'MASTER SEO'!O5</f>
+        <v/>
+      </c>
+      <c r="B5" s="2">
+        <f>'MASTER SEO'!A5</f>
+        <v/>
+      </c>
+      <c r="C5" s="2">
+        <f>'MASTER SEO'!C5</f>
+        <v/>
+      </c>
+      <c r="D5" s="2">
+        <f>'MASTER SEO'!I5</f>
+        <v/>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Revisão programada</t>
+        </is>
+      </c>
+      <c r="F5" s="2">
+        <f>'MASTER SEO'!K5</f>
+        <v/>
+      </c>
+      <c r="G5" s="2">
+        <f>'MASTER SEO'!L5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4">
+        <f>'MASTER SEO'!O6</f>
+        <v/>
+      </c>
+      <c r="B6" s="2">
+        <f>'MASTER SEO'!A6</f>
+        <v/>
+      </c>
+      <c r="C6" s="2">
+        <f>'MASTER SEO'!C6</f>
+        <v/>
+      </c>
+      <c r="D6" s="2">
+        <f>'MASTER SEO'!I6</f>
+        <v/>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Revisão programada</t>
+        </is>
+      </c>
+      <c r="F6" s="2">
+        <f>'MASTER SEO'!K6</f>
+        <v/>
+      </c>
+      <c r="G6" s="2">
+        <f>'MASTER SEO'!L6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4">
+        <f>'MASTER SEO'!O7</f>
+        <v/>
+      </c>
+      <c r="B7" s="2">
+        <f>'MASTER SEO'!A7</f>
+        <v/>
+      </c>
+      <c r="C7" s="2">
+        <f>'MASTER SEO'!C7</f>
+        <v/>
+      </c>
+      <c r="D7" s="2">
+        <f>'MASTER SEO'!I7</f>
+        <v/>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Revisão programada</t>
+        </is>
+      </c>
+      <c r="F7" s="2">
+        <f>'MASTER SEO'!K7</f>
+        <v/>
+      </c>
+      <c r="G7" s="2">
+        <f>'MASTER SEO'!L7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4">
+        <f>'MASTER SEO'!O8</f>
+        <v/>
+      </c>
+      <c r="B8" s="2">
+        <f>'MASTER SEO'!A8</f>
+        <v/>
+      </c>
+      <c r="C8" s="2">
+        <f>'MASTER SEO'!C8</f>
+        <v/>
+      </c>
+      <c r="D8" s="2">
+        <f>'MASTER SEO'!I8</f>
+        <v/>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Revisão programada</t>
+        </is>
+      </c>
+      <c r="F8" s="2">
+        <f>'MASTER SEO'!K8</f>
+        <v/>
+      </c>
+      <c r="G8" s="2">
+        <f>'MASTER SEO'!L8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4">
+        <f>'MASTER SEO'!O9</f>
+        <v/>
+      </c>
+      <c r="B9" s="2">
+        <f>'MASTER SEO'!A9</f>
+        <v/>
+      </c>
+      <c r="C9" s="2">
+        <f>'MASTER SEO'!C9</f>
+        <v/>
+      </c>
+      <c r="D9" s="2">
+        <f>'MASTER SEO'!I9</f>
+        <v/>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Revisão programada</t>
+        </is>
+      </c>
+      <c r="F9" s="2">
+        <f>'MASTER SEO'!K9</f>
+        <v/>
+      </c>
+      <c r="G9" s="2">
+        <f>'MASTER SEO'!L9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4">
+        <f>'MASTER SEO'!O10</f>
+        <v/>
+      </c>
+      <c r="B10" s="2">
+        <f>'MASTER SEO'!A10</f>
+        <v/>
+      </c>
+      <c r="C10" s="2">
+        <f>'MASTER SEO'!C10</f>
+        <v/>
+      </c>
+      <c r="D10" s="2">
+        <f>'MASTER SEO'!I10</f>
+        <v/>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Revisão programada</t>
+        </is>
+      </c>
+      <c r="F10" s="2">
+        <f>'MASTER SEO'!K10</f>
+        <v/>
+      </c>
+      <c r="G10" s="2">
+        <f>'MASTER SEO'!L10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4">
+        <f>'MASTER SEO'!O11</f>
+        <v/>
+      </c>
+      <c r="B11" s="2">
+        <f>'MASTER SEO'!A11</f>
+        <v/>
+      </c>
+      <c r="C11" s="2">
+        <f>'MASTER SEO'!C11</f>
+        <v/>
+      </c>
+      <c r="D11" s="2">
+        <f>'MASTER SEO'!I11</f>
+        <v/>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Revisão programada</t>
+        </is>
+      </c>
+      <c r="F11" s="2">
+        <f>'MASTER SEO'!K11</f>
+        <v/>
+      </c>
+      <c r="G11" s="2">
+        <f>'MASTER SEO'!L11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4">
+        <f>'MASTER SEO'!O12</f>
+        <v/>
+      </c>
+      <c r="B12" s="2">
+        <f>'MASTER SEO'!A12</f>
+        <v/>
+      </c>
+      <c r="C12" s="2">
+        <f>'MASTER SEO'!C12</f>
+        <v/>
+      </c>
+      <c r="D12" s="2">
+        <f>'MASTER SEO'!I12</f>
+        <v/>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Revisão programada</t>
+        </is>
+      </c>
+      <c r="F12" s="2">
+        <f>'MASTER SEO'!K12</f>
+        <v/>
+      </c>
+      <c r="G12" s="2">
+        <f>'MASTER SEO'!L12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4">
+        <f>'MASTER SEO'!O13</f>
+        <v/>
+      </c>
+      <c r="B13" s="2">
+        <f>'MASTER SEO'!A13</f>
+        <v/>
+      </c>
+      <c r="C13" s="2">
+        <f>'MASTER SEO'!C13</f>
+        <v/>
+      </c>
+      <c r="D13" s="2">
+        <f>'MASTER SEO'!I13</f>
+        <v/>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Revisão programada</t>
+        </is>
+      </c>
+      <c r="F13" s="2">
+        <f>'MASTER SEO'!K13</f>
+        <v/>
+      </c>
+      <c r="G13" s="2">
+        <f>'MASTER SEO'!L13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B14" t="n">
+        <v>14</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>como escolher fogão mesa de vidro</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>/como-escolher-fogao-mesa-de-vidro/</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Revisar após publicação + dados GSC</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Planejado</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B15" t="n">
+        <v>15</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>fogão mesa de vidro custo benefício</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>/fogao-mesa-de-vidro-custo-beneficio/</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Revisar após publicação + dados GSC</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Planejado</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1887,22 +2202,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Data</t>
@@ -1961,17 +2276,17 @@
       <c r="B2" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>fogao consul mesa de vidro</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>/review-fogao-mesa-de-vidro-consul/</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Otimização SEO on-page</t>
         </is>
@@ -1982,285 +2297,91 @@
       <c r="G2" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Meta description, abertura, desambiguação, H2s, tabela, FAQ e veredito</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Aguardando nova medição</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Build aprovado; aguardar indexação.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>melhor fogao 5 bocas</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>SEO on-page — Etapa 1</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Title + meta description da Home. Title: Melhores fogões 5 bocas em 2026: ranking atualizado | Casa Prática Eletro. Description: Ranking e recomendação dos melhores fogões 5 bocas em 2026: Electrolux FE5IG, Brastemp BFS5NCR e Consul CFS5NAB. Compare os modelos e decida a compra. OG/Twitter derivados. H1, ranking, CTAs, canonical e redirects preservados. Build 29 páginas, exit 0. Sem commit/push/deploy.</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Aguardando nova medição</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>Home consolidada como dona da intenção 'melhor fogão 5 bocas'. Etapa 1 limitada a title + meta description; OG/Twitter derivados. Hub /melhores/melhor-fogao-5-bocas/ permanece 301 → /. Não reabrir o hub por persistência histórica no Semrush. Aguardar recrawl/nova medição antes de nova intervenção.</t>
+      <c r="A3" s="6" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>como escolher fogão mesa de vidro</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>/como-escolher-fogao-mesa-de-vidro/</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Decisão estratégica</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Incluída no MASTER após cruzamento concorrentes + GSC + SERP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Nova página aprovada para planejamento; volume específico não confirmado no lote.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n">
-        <v>46268</v>
+      <c r="A4" s="6" t="n">
+        <v>46270</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>tamanho fogão 5 bocas</t>
+          <t>fogão mesa de vidro custo benefício</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>/como-escolher-fogao-5-bocas/</t>
+          <t>/fogao-mesa-de-vidro-custo-beneficio/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SEO on-page — Etapa 1 + conteúdo</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>31</v>
-      </c>
-      <c r="G4" t="n">
-        <v>31</v>
+          <t>Decisão estratégica</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Title ajustado (prioriza tamanho/medidas); meta description com medidas típicas (75-80 cm / 60-70 cm / ~90 cm); resposta direta e tabela inseridas no step 1; orientação sobre conferência de medidas por modelo/instalação; H1 e estrutura preservados; dados reutilizados do blog fogao-5-bocas-reduz-espaco-cozinha. Build 29 págs, exit 0.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Alteração realizada — aguardando nova medição</t>
+          <t>Incluída no MASTER após cruzamento concorrentes + GSC + SERP</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Variação volume: keyword principal 590 (tamanho fogão 5 bocas) + variação 90 (tamanho do fogão 5 bocas). Próxima revisão: ~01/10/2026. Sem commit/push/deploy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>melhor fogao 5 bocas custo beneficio</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>/fogao-5-bocas-custo-beneficio/</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SEO on-page — Etapa 1</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>62</v>
-      </c>
-      <c r="G5" t="n">
-        <v>62</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Title e meta description da página otimizados para consolidar a intenção de custo-benefício/preço-performance.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Alteração realizada</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Home permanece dona de “melhores fogões 5 bocas”; esta URL permanece dona da intenção específica de custo-benefício. Aguardar recrawl/GSC antes de nova intervenção.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B6" t="n">
-        <v>8</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>fogão com mesa de vidro ou inox</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>/blog/fogao-mesa-de-vidro-ou-inox/</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>SEO on-page — Etapa 1</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>title e meta description</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Alteração realizada</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>comparação vidro × inox permanece separada do ranking de melhores fogões com mesa de vidro; aguardar recrawl/GSC antes de nova intervenção.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B7" t="n">
-        <v>13</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>fogão com mesa de vidro é perigoso</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>/blog/fogao-mesa-de-vidro-seguro/</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SEO on-page — Etapa 1</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>13</v>
-      </c>
-      <c r="G7" t="n">
-        <v>13</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Title + meta description</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Alteração realizada</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Consolidação da intenção de segurança/risco; comparativo vidro × inox e hub de ranking permanecem com suas respectivas intenções.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B8" t="n">
-        <v>9</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>fogão 4 bocas custo benefício</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>/fogao-4-bocas-custo-beneficio/</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>SEO on-page — Etapa 2</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>46</v>
-      </c>
-      <c r="G8" t="n">
-        <v>46</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>FAQ visível + FAQPage</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Alteração realizada</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Etapa 2: FAQ visível + FAQPage sobre custo-benefício. Title/H1/meta/canonical preservados. Não altera ownership do hub melhor fogão 4 bocas. Aguardar GSC.</t>
+          <t>Nova página aprovada para planejamento; volume específico não confirmado no lote.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -2270,10 +2391,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -2290,172 +2411,567 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>MASTER SEO</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Estado atual das keywords, URLs, decisões e prioridades.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>ENTRADAS SEMRUSH</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Local para acrescentar novas exportações sem apagar o histórico.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>HISTÓRICO</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Registro de alterações, posições antes/depois e resultados.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>CALENDÁRIO</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Revisões programadas; a próxima revisão é calculada 28 dias após uma alteração.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>REGRA</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Antes de criar nova página, verificar se uma URL existente pode ser a dona da intenção.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>FLUXO</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Semrush → Entradas → classificação → Master → ação → Histórico → revisão.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>CURSOR</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>A planilha pode ser colocada no projeto e usada como fonte operacional para análises futuras.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>DADOS INICIAIS</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>São os grupos/intensões já identificados; campos não confirmados permanecem vazios.</t>
         </is>
       </c>
     </row>
+  </sheetData>
+  <autoFilter ref="A1:B9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>ESTUDO DE CAMPO — DECISÃO DE CONTEÚDO</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="n"/>
+      <c r="C1" s="7" t="n"/>
+      <c r="D1" s="7" t="n"/>
+      <c r="E1" s="7" t="n"/>
+      <c r="F1" s="7" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Encontrar novas oportunidades com demanda, intenção comercial, encaixe arquitetural e caminho de monetização.</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n"/>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>EVIDÊNCIA</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>CONCLUSÃO</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>IMPLICAÇÃO</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>FONTE</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n"/>
+      <c r="F5" s="9" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Concorrente editorial — Melhores Fogões</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Páginas de decisão (4/5 bocas, custo-benefício, cooktops) concentram tráfego estimado e keywords comerciais.</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Modelo editorial de decisão é validado no mercado.</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Export Top Pages 2026-09-04</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Concorrente editorial — Qual Melhor Comprar</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Cluster de fogões aparece em várias intenções: melhor, 4/5 bocas, marca, indução, grill e inox.</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Subintenções são tratadas como caminhos distintos.</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Export Positions 2026-09-04</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Concorrente editorial — Casa dos Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Aparecem páginas específicas para mesa de vidro, medidas, marcas e instalação.</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Critérios pré-compra e dúvidas específicas têm espaço editorial.</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Export Positions 2026-09-04</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>GSC Casa Prática — mesa de vidro</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>183 impressões posição 18,95; 48/11,54; 42/21,48; 29/12,72; 28/9,71; 19/11,84 em consultas de segurança/cuidados.</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>É o cluster com convergência mais forte entre demanda real e arquitetura.</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>GSC 3 meses — Consultas/Páginas</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+    </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>TABELAS</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>MasterSEO, EntradasSemrush e HistoricoAcoes são Tabelas Excel: filtros e fórmulas acompanham novas linhas (Tab na última célula, ou colar imediatamente abaixo).</t>
-        </is>
-      </c>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>GSC Casa Prática — reviews</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Reviews Consul/Electrolux/Brastemp aparecem em posições aproximadamente 4–8 em várias consultas de SKU.</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Formato review já tem aderência; não é necessário criar uma nova arquitetura comercial.</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>GSC 3 meses — Páginas/Consultas</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>CALENDÁRIO (uso)</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Agenda automática via FILTER. Mostra somente registros do Master com data de próxima revisão. Não editar. URL dona vazia aparece em branco (nunca como 0).</t>
-        </is>
-      </c>
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>GSC Casa Prática — 5 bocas</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Variantes de 'melhor fogão 5 bocas' acumulam impressões, mas ficam aproximadamente em posição 60+ e têm conflito histórico de URL.</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Não criar segunda money page; preservar ownership da Home.</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>GSC + mapa arquitetural</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>POSIÇÕES vs AÇÕES</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Histórico de posições (exportações Semrush) = ENTRADAS SEMRUSH. Histórico de ações SEO = HISTÓRICO. Não misturar nem sobrescrever.</t>
-        </is>
-      </c>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>SERP — 'como escolher fogão com mesa de vidro'</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>AI Overview, vídeos, PAA, editoriais e produtos; intenção informacional→comercial.</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Valida satélite de critérios, sem transformar em novo ranking.</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>SERP observada em janela anônima</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>COMO IMPORTAR SEMRUSH</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>1) Criar um ID de lote novo (SM-AAAA-MM-DD; se houver duas exportações no mesmo dia, SM-AAAA-MM-DD-2). 2) Colar as keywords como NOVAS linhas na tabela EntradasSemrush. 3) Preencher ID do lote, data, keyword, posição, volume, KD, intenção, URL encontrada, SERP Features. 4) Nunca apagar ou sobrescrever lotes anteriores. 5) Depois classificar no MASTER: copiar posição atual para posição anterior e gravar a nova posição.</t>
-        </is>
-      </c>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>SERP — 'fogão com mesa de vidro vale a pena'</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>AI Overview, prós/contras, PAA, vídeos, editoriais e produtos; Casa Prática já aparece com comparativo vidro/inox.</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Não criar duplicata de vale a pena/comparativo; usar como jornada.</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>SERP observada em janela anônima</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>NOVA KEYWORD NO MASTER</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Incluir na tabela MasterSEO (linha nova). Preencher ID sequencial, silo, keyword, intenção, decisão, prioridade e status. Próxima revisão e variação de posição calculam sozinhas. O calendário inclui a linha quando Última alteração for preenchida.</t>
-        </is>
-      </c>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>SERP — 'melhor fogão com mesa de vidro'</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Ranking e produtos dominam; hub de mesa de vidro já existe.</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Não criar segundo ranking; fortalecer satélites que alimentem o hub.</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>SERP observada em janela anônima</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>URLS</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>URL atual = URL encontrada no Semrush/SERP (mesmo se for rota antiga/301). URL dona/alvo = URL dona atual no projeto, quando comprovada. Não sobrescrever a URL encontrada pelo Semrush.</t>
-        </is>
-      </c>
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>DECISÃO FINAL</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>PRIORIDADE</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>MOTIVO</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>CRIAR</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>/como-escolher-fogao-mesa-de-vidro/</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>1 — Alta</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Fecha o estágio de critérios pré-compra do cluster mesa de vidro; baixa canibalização se não disputar 'melhor'.</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>CRIAR</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>/fogao-mesa-de-vidro-custo-beneficio/</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>2 — Alta</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Fecha o estágio de valor/preço do cluster; complementar ao satélite de critérios e ao hub.</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>NÃO CRIAR AGORA</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Nova página 'melhor fogão 5 bocas'</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Bloqueado</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Home é a dona arquitetural; risco alto de canibalização.</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>NÃO CRIAR AGORA</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Nova página 'fogão Consul é bom'</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Bloqueado</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Review Consul mesa de vidro já captura o termo e está em monitoramento.</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>NÃO CRIAR AGORA</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Nova página 'melhor fogão mesa de vidro'</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Bloqueado</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Hub já existe; nova URL duplicaria a intenção.</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
